--- a/output/pdf_financials_xlsx/ARWY.xlsx
+++ b/output/pdf_financials_xlsx/ARWY.xlsx
@@ -1924,13 +1924,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.257463</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.328555</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.379155</v>
       </c>
     </row>
     <row r="93">
@@ -3009,7 +3009,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -3339,7 +3343,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>1.257463</v>
       </c>

--- a/output/pdf_financials_xlsx/ARWY.xlsx
+++ b/output/pdf_financials_xlsx/ARWY.xlsx
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.014835</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001539</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -869,10 +869,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-8.096781</v>
+        <v>-8.111616</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.426989</v>
+        <v>-2.428528</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.32729</v>
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-8.095419</v>
+        <v>-8.110253999999999</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.424846</v>
+        <v>-2.426385</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.32729</v>
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-13554.48974466304</v>
+        <v>-13579.32858936793</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-1911.494923377688</v>
+        <v>-1912.708109982973</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>-68.36201854791545</v>
@@ -978,7 +978,7 @@
         <v>0.000398</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.006628</v>
       </c>
     </row>
     <row r="35">
@@ -1010,7 +1010,7 @@
         <v>0.000398</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.006628</v>
       </c>
     </row>
     <row r="37">
@@ -1202,7 +1202,7 @@
         <v>0.024081</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.031567</v>
+        <v>0.024939</v>
       </c>
     </row>
     <row r="49">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">

--- a/output/pdf_financials_xlsx/ARWY.xlsx
+++ b/output/pdf_financials_xlsx/ARWY.xlsx
@@ -1458,13 +1458,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.147595</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.627887</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.798241</v>
       </c>
     </row>
     <row r="65">
@@ -1506,13 +1506,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.004998</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.03875</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.017971</v>
       </c>
     </row>
     <row r="68">
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.006539</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.006539</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-1.692096</v>
+        <v>-1.698635</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.675967</v>
@@ -4772,7 +4772,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E67" s="5" t="n">
         <v>-0.006539</v>
       </c>
@@ -4838,7 +4842,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E69" s="5" t="n">
         <v>1.657351</v>
       </c>
